--- a/api/templates/export/reporters/en.xlsx
+++ b/api/templates/export/reporters/en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/Sites/SystemOne/aspect/api/templates/export/reporters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\export\reporters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1610E93F-C6E3-A340-9CA8-09633B124BB7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88022F94-019B-419C-A559-44412C3EA25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="3380" windowWidth="23540" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reporters" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -221,9 +221,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -233,19 +230,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,43 +551,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.33203125" style="6" customWidth="1"/>
-    <col min="2" max="5" width="16.1640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="15" customWidth="1"/>
-    <col min="7" max="8" width="16.1640625" style="14" customWidth="1"/>
-    <col min="9" max="16384" width="9.1640625" style="1"/>
+    <col min="2" max="8" width="16.109375" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:8" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="9" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -611,39 +597,39 @@
       <c r="E5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
